--- a/Treinamento/Cópia de Cadastro_Restricao (1).xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao (1).xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE04122-R0261031\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC18219C-B191-4B3A-86E6-459619F3E6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872BCE98-2387-442F-8D73-30A6D04E55A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19560" windowHeight="9975" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -65,34 +64,22 @@
     <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
   </si>
   <si>
-    <t>Jacqueline Coelho</t>
-  </si>
-  <si>
-    <t>QAV8J88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8AJBA3CD4L1636567 </t>
-  </si>
-  <si>
-    <t>SFE3J50</t>
-  </si>
-  <si>
-    <t>LGXCF6CD5R2006605</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rodrigo Belisário </t>
   </si>
   <si>
-    <t>RFA3C66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9C2KC2200LR129972 </t>
-  </si>
-  <si>
-    <t>LQQ6066</t>
-  </si>
-  <si>
-    <t>8A1FC1415DL504837</t>
+    <t>BZB3666</t>
+  </si>
+  <si>
+    <t>WV1DA22H7LA003060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sem placa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">98PACM370SB157187 </t>
+  </si>
+  <si>
+    <t>Weldja</t>
   </si>
 </sst>
 </file>
@@ -595,7 +582,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45694</v>
+        <v>45695</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -609,13 +596,10 @@
       <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4">
-        <v>131240070</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>45694</v>
+        <v>45695</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>12</v>
@@ -629,58 +613,17 @@
       <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="4">
-        <v>131246968</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>45694</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4">
-        <v>131249549</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>45694</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="4">
-        <v>131254687</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>

--- a/Treinamento/Cópia de Cadastro_Restricao (1).xlsx
+++ b/Treinamento/Cópia de Cadastro_Restricao (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE02604-R0257456\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66BDC6F-D39F-4257-A8FC-B7AD59DFA19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C013DB-B089-4FA7-8460-2430600BA8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B2F5E845-3AAD-41EC-86D8-A72C6B99931E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>DATA DA IDENTIFICAÇÃO DO CASO</t>
   </si>
@@ -65,37 +65,49 @@
     <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
   </si>
   <si>
-    <t>Jacqueline Coelho</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rodrigo Belisário </t>
   </si>
   <si>
-    <t>QEM9198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8AJBA3CD0K1614872 </t>
-  </si>
-  <si>
-    <t>IYL0838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8AC906133JE143147  </t>
-  </si>
-  <si>
     <t>Weldja</t>
   </si>
   <si>
-    <t>RDZ5912</t>
-  </si>
-  <si>
-    <t>9BWAB45Z4M4013769</t>
-  </si>
-  <si>
-    <t>OQE0A26</t>
-  </si>
-  <si>
-    <t>93ZA90D00D8560806</t>
+    <t xml:space="preserve">SFJ0D82 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9535E6TBXSR007913 </t>
+  </si>
+  <si>
+    <t>AWC2735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9531M62P5CR257611 </t>
+  </si>
+  <si>
+    <t>RYZ7A75</t>
+  </si>
+  <si>
+    <t>988675AJDSKM92560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sem placa </t>
+  </si>
+  <si>
+    <t>9886111LGSK643409</t>
+  </si>
+  <si>
+    <t>Priscila Oliveira</t>
+  </si>
+  <si>
+    <t>QPX6262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3VVJ465N3KM037092 </t>
+  </si>
+  <si>
+    <t>TLU6C46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">988591253RKR81580 </t>
   </si>
 </sst>
 </file>
@@ -598,7 +610,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>11</v>
@@ -613,12 +625,12 @@
         <v>9</v>
       </c>
       <c r="F2" s="4">
-        <v>132054936</v>
+        <v>132067967</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>13</v>
@@ -630,57 +642,91 @@
         <v>8</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4">
-        <v>132053887</v>
+        <v>132071178</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="4">
-        <v>132055174</v>
+        <v>132073803</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4">
+        <v>132074196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>45756</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="4">
-        <v>132057838</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
+      <c r="F6" s="4">
+        <v>132076392</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3">
+        <v>45756</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="4">
+        <v>132083609</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
